--- a/SGC-CKN/Excel/eefa7183-4dbb-46b4-a821-44a9638378ce_Hạng_mục__Trung_tâm_văn_hóa_thể_thao__trung_tâm_hội_nghị__nhà_hát_P336_D1200_03-04-2026.xlsx
+++ b/SGC-CKN/Excel/eefa7183-4dbb-46b4-a821-44a9638378ce_Hạng_mục__Trung_tâm_văn_hóa_thể_thao__trung_tâm_hội_nghị__nhà_hát_P336_D1200_03-04-2026.xlsx
@@ -163,7 +163,7 @@
   </si>
   <si>
     <t xml:space="preserve">00:05
-02/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -173,7 +173,7 @@
   </si>
   <si>
     <t xml:space="preserve">00:35
-02/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -183,7 +183,7 @@
   </si>
   <si>
     <t xml:space="preserve">01:40
-02/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>10</t>
@@ -193,7 +193,7 @@
   </si>
   <si>
     <t xml:space="preserve">03:30
-02/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>11</t>
@@ -203,7 +203,7 @@
   </si>
   <si>
     <t xml:space="preserve">06:05
-02/04/2026</t>
+03/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
